--- a/data/trans_bre/P1402-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P1402-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1,4</t>
+          <t>2,09</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,98</t>
+          <t>-0,26; 5,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,98</t>
+          <t>-2,23; 4,1</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 3,97</t>
+          <t>-4,29; 3,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 4,94</t>
+          <t>-1,48; 5,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 47,12</t>
+          <t>-2,03; 47,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,95; 25,72</t>
+          <t>-11,75; 26,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,97; 22,96</t>
+          <t>-19,43; 20,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-10,87; 28,6</t>
+          <t>-7,32; 32,6</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-2,89</t>
+          <t>-3,07</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-42,42%</t>
+          <t>-40,26%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,2</t>
+          <t>-2,17; 0,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 0,61</t>
+          <t>-1,83; 0,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,16; -0,17</t>
+          <t>-3,1; -0,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-4,56; -0,67</t>
+          <t>-4,27; -1,88</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-56,42; 10,39</t>
+          <t>-57,75; 4,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-42,61; 19,54</t>
+          <t>-43,52; 21,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-46,06; -3,31</t>
+          <t>-45,19; -3,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-59,44; -18,57</t>
+          <t>-50,96; -27,48</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,0</t>
+          <t>-4,1</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-59,67%</t>
+          <t>-58,67%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 1,27</t>
+          <t>-2,28; 1,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,36; 0,97</t>
+          <t>-3,3; 0,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 0,68</t>
+          <t>-4,2; 0,45</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,36; -2,19</t>
+          <t>-6,3; -2,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-73,88; 95,18</t>
+          <t>-72,39; 77,23</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-82,43; 83,52</t>
+          <t>-82,23; 68,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-72,7; 22,42</t>
+          <t>-69,69; 17,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-74,05; -37,96</t>
+          <t>-74,07; -37,06</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-1,51</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-16,97%</t>
+          <t>-16,15%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 2,3</t>
+          <t>-0,02; 2,24</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 2,51</t>
+          <t>-0,27; 2,36</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,08</t>
+          <t>-1,71; 1,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 0,57</t>
+          <t>-2,59; -0,31</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 43,93</t>
+          <t>-0,66; 42,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 36,32</t>
+          <t>-3,21; 34,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 13,59</t>
+          <t>-18,0; 12,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-30,8; 6,37</t>
+          <t>-25,72; -3,63</t>
         </is>
       </c>
     </row>
